--- a/Collections/EURO/Slovenia/#EURO#Slovenia#Commemorative#[2007-present]#UNC.xlsx
+++ b/Collections/EURO/Slovenia/#EURO#Slovenia#Commemorative#[2007-present]#UNC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF3B10B-BC63-4095-BDB0-1359E9E3F44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C039E6E7-FFDA-499A-B3AF-704838DB3654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,7 +222,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="59">
   <si>
     <t>Year</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>Subtype_2#Special_marks_1</t>
+  </si>
+  <si>
+    <t>150th Anniversary - Birth of Ivan Cankar</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -2361,6 +2364,55 @@
         <v/>
       </c>
     </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="18">
+        <v>0</v>
+      </c>
+      <c r="P24" s="6" t="str">
+        <f t="shared" ref="P24" si="5">IF(OR(AND(K24&gt;1,K24&lt;&gt;"-"),AND(L24&gt;1,L24&lt;&gt;"-"),AND(M24&gt;1,M24&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:J2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
@@ -2371,8 +2423,23 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="N13">
-    <cfRule type="containsText" dxfId="24" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N13))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M14">
+    <cfRule type="containsText" dxfId="23" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M14))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="46">
       <colorScale>
@@ -2385,9 +2452,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="23" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M14))))</formula>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="containsText" dxfId="22" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="44">
       <colorScale>
@@ -2400,9 +2467,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5">
-    <cfRule type="containsText" dxfId="22" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K5))))</formula>
+  <conditionalFormatting sqref="M12">
+    <cfRule type="containsText" dxfId="21" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M12))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="42">
       <colorScale>
@@ -2415,11 +2482,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M12">
-    <cfRule type="containsText" dxfId="21" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M12))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="N16">
+    <cfRule type="containsText" dxfId="20" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(N16))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2430,9 +2497,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N16">
-    <cfRule type="containsText" dxfId="20" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(N16))))</formula>
+  <conditionalFormatting sqref="N15">
+    <cfRule type="containsText" dxfId="19" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(N15))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
       <colorScale>
@@ -2445,9 +2512,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N15">
-    <cfRule type="containsText" dxfId="19" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(N15))))</formula>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="containsText" dxfId="18" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
       <colorScale>
@@ -2460,9 +2527,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="containsText" dxfId="18" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K6))))</formula>
+  <conditionalFormatting sqref="M11">
+    <cfRule type="containsText" dxfId="17" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M11))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
       <colorScale>
@@ -2475,9 +2542,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11">
-    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M11))))</formula>
+  <conditionalFormatting sqref="L10">
+    <cfRule type="containsText" dxfId="16" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L10))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
       <colorScale>
@@ -2490,9 +2557,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10">
-    <cfRule type="containsText" dxfId="16" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(L10))))</formula>
+  <conditionalFormatting sqref="M9">
+    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
       <colorScale>
@@ -2505,9 +2572,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9">
-    <cfRule type="containsText" dxfId="15" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M9))))</formula>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="containsText" dxfId="14" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
       <colorScale>
@@ -2520,9 +2587,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
-    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M8))))</formula>
+  <conditionalFormatting sqref="L4">
+    <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
       <colorScale>
@@ -2535,9 +2602,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4">
-    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(L4))))</formula>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
       <colorScale>
@@ -2550,9 +2617,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M20">
-    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M20))))</formula>
+  <conditionalFormatting sqref="M17">
+    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M17))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
       <colorScale>
@@ -2565,9 +2632,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M17">
-    <cfRule type="containsText" dxfId="11" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M17))))</formula>
+  <conditionalFormatting sqref="M18">
+    <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M18))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
@@ -2580,9 +2647,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M18">
-    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M18))))</formula>
+  <conditionalFormatting sqref="N19">
+    <cfRule type="containsText" dxfId="9" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(N19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
@@ -2595,9 +2662,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N19">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(N19))))</formula>
+  <conditionalFormatting sqref="N21">
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(N21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
       <colorScale>
@@ -2610,9 +2677,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N21">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(N21))))</formula>
+  <conditionalFormatting sqref="O22">
+    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(O22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
       <colorScale>
@@ -2625,9 +2692,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O22">
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(O22))))</formula>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
       <colorScale>
@@ -2640,9 +2707,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
@@ -2655,11 +2722,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="O23">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(O23))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2670,9 +2737,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O23">
+  <conditionalFormatting sqref="O24">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(O23))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(O24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
